--- a/data/informes/cuadro_10_7.xlsx
+++ b/data/informes/cuadro_10_7.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>12186709.77</v>
+        <v>12480234.36</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
@@ -539,13 +539,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>6333783.35</v>
+        <v>6358956.81</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>62003881.48</v>
+        <v>59846857.85</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>80524374.59999999</v>
+        <v>78686049.02</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>684287.28</v>
+        <v>977811.92</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>0</v>
@@ -567,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>538630.01</v>
+        <v>563803.48</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>19340361.8</v>
+        <v>23914993.77</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>20563279.09</v>
+        <v>25456609.17</v>
       </c>
     </row>
     <row r="6">
@@ -598,10 +598,10 @@
         <v>74033.66</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>18470047.35</v>
+        <v>23321034.06</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>18554585.24</v>
+        <v>23405571.95</v>
       </c>
     </row>
     <row r="7">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>673783.05</v>
+        <v>967307.6899999999</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>0</v>
@@ -623,13 +623,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>464596.35</v>
+        <v>489769.82</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>870314.45</v>
+        <v>593959.71</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>2008693.85</v>
+        <v>2051037.22</v>
       </c>
     </row>
     <row r="8">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>11437078.79</v>
+        <v>11437078.74</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>0</v>
@@ -651,13 +651,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>3224577.31</v>
+        <v>3224577.3</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>39500954.5</v>
+        <v>32773448.28</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>54162610.6</v>
+        <v>47435104.32</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1462078.74</v>
+        <v>1462078.73</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>0</v>
@@ -679,13 +679,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>2555281.59</v>
+        <v>2555281.58</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>2619013.88</v>
+        <v>2248152.16</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>6636374.21</v>
+        <v>6265512.47</v>
       </c>
     </row>
     <row r="10">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>9975000.050000001</v>
+        <v>9975000.01</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>669295.72</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>28078433.86</v>
+        <v>25376254.06</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>38722729.63</v>
+        <v>36020549.79</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>8493344.800000001</v>
+        <v>8493344.77</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>0</v>
@@ -738,10 +738,10 @@
         <v>557855.71</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>22460586.68</v>
+        <v>20406701.63</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>31511787.19</v>
+        <v>29457902.11</v>
       </c>
     </row>
     <row r="12">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>3633414.31</v>
+        <v>3633414.29</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>0</v>
@@ -766,10 +766,10 @@
         <v>66604.27</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>7221878.96</v>
+        <v>6559634.62</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10921897.54</v>
+        <v>10259653.18</v>
       </c>
     </row>
     <row r="13">
@@ -794,10 +794,10 @@
         <v>440150.59</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>12741443.53</v>
+        <v>11410167.78</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>17352882.13</v>
+        <v>16021606.38</v>
       </c>
     </row>
     <row r="14">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>606644.26</v>
+        <v>606644.25</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>0</v>
@@ -822,10 +822,10 @@
         <v>51100.85</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>2376480.86</v>
+        <v>2316115.9</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>3034225.97</v>
+        <v>2973861</v>
       </c>
     </row>
     <row r="15">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>1375919.13</v>
+        <v>1375919.12</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>0</v>
@@ -878,10 +878,10 @@
         <v>98649.8</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>5580397.69</v>
+        <v>4932102.94</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>7054966.62</v>
+        <v>6406671.86</v>
       </c>
     </row>
     <row r="17">
@@ -906,10 +906,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4540347.48</v>
+        <v>3825544.76</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>4540347.48</v>
+        <v>3825544.76</v>
       </c>
     </row>
     <row r="18">
@@ -934,10 +934,10 @@
         <v>2570576.02</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>3162565.18</v>
+        <v>3158415.8</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>5798484.9</v>
+        <v>5794335.52</v>
       </c>
     </row>
     <row r="19">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>12186709.77</v>
+        <v>12480234.36</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>0</v>
@@ -959,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>6333783.35</v>
+        <v>6358956.81</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>62003881.48</v>
+        <v>59846857.85</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>80524374.59999999</v>
+        <v>78686049.02</v>
       </c>
     </row>
   </sheetData>

--- a/data/informes/cuadro_10_7.xlsx
+++ b/data/informes/cuadro_10_7.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>12480234.36</v>
+        <v>12448251.11</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
@@ -539,13 +539,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>6358956.81</v>
+        <v>6354989.19</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>59846857.85</v>
+        <v>65166907.89</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>78686049.02</v>
+        <v>83970148.19</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>977811.92</v>
+        <v>945828.6800000001</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>0</v>
@@ -567,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>563803.48</v>
+        <v>559835.85</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>23914993.77</v>
+        <v>23509179.54</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>25456609.17</v>
+        <v>25014844.07</v>
       </c>
     </row>
     <row r="6">
@@ -598,10 +598,10 @@
         <v>74033.66</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>23321034.06</v>
+        <v>22929944.04</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>23405571.95</v>
+        <v>23014481.93</v>
       </c>
     </row>
     <row r="7">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>967307.6899999999</v>
+        <v>935324.45</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>0</v>
@@ -623,13 +623,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>489769.82</v>
+        <v>485802.19</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>593959.71</v>
+        <v>579235.5</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>2051037.22</v>
+        <v>2000362.14</v>
       </c>
     </row>
     <row r="8">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>11437078.74</v>
+        <v>11437078.73</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>0</v>
@@ -651,13 +651,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>3224577.3</v>
+        <v>3224577.31</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>32773448.28</v>
+        <v>38499312.55</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>47435104.32</v>
+        <v>53160968.59</v>
       </c>
     </row>
     <row r="9">
@@ -679,13 +679,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>2555281.58</v>
+        <v>2555281.59</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>2248152.16</v>
+        <v>2570238.77</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>6265512.47</v>
+        <v>6587599.09</v>
       </c>
     </row>
     <row r="10">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>9975000.01</v>
+        <v>9975000</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -710,10 +710,10 @@
         <v>669295.72</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>25376254.06</v>
+        <v>27674789</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>36020549.79</v>
+        <v>38319084.72</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>8493344.77</v>
+        <v>8493344.75</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>0</v>
@@ -738,10 +738,10 @@
         <v>557855.71</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>20406701.63</v>
+        <v>22155034.11</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>29457902.11</v>
+        <v>31206234.57</v>
       </c>
     </row>
     <row r="12">
@@ -766,10 +766,10 @@
         <v>66604.27</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>6559634.62</v>
+        <v>7126307.17</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10259653.18</v>
+        <v>10826325.73</v>
       </c>
     </row>
     <row r="13">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>4171288.01</v>
+        <v>4171287.99</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>0</v>
@@ -794,10 +794,10 @@
         <v>440150.59</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>11410167.78</v>
+        <v>12541966.45</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>16021606.38</v>
+        <v>17153405.03</v>
       </c>
     </row>
     <row r="14">
@@ -822,10 +822,10 @@
         <v>51100.85</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>2316115.9</v>
+        <v>2365977.16</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>2973861</v>
+        <v>3023722.26</v>
       </c>
     </row>
     <row r="15">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>1375919.12</v>
+        <v>1375919.13</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>0</v>
@@ -878,10 +878,10 @@
         <v>98649.8</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>4932102.94</v>
+        <v>5482305.4</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>6406671.86</v>
+        <v>6956874.33</v>
       </c>
     </row>
     <row r="17">
@@ -906,10 +906,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>3825544.76</v>
+        <v>4680836.36</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>3825544.76</v>
+        <v>4680836.36</v>
       </c>
     </row>
     <row r="18">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>12480234.36</v>
+        <v>12448251.11</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>0</v>
@@ -959,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>6358956.81</v>
+        <v>6354989.19</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>59846857.85</v>
+        <v>65166907.89</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>78686049.02</v>
+        <v>83970148.19</v>
       </c>
     </row>
   </sheetData>

--- a/data/informes/cuadro_10_7.xlsx
+++ b/data/informes/cuadro_10_7.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>12448251.11</v>
+        <v>17442565.9</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
@@ -539,13 +539,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>6354989.19</v>
+        <v>9410124.939999999</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>65166907.89</v>
+        <v>122657778.56</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>83970148.19</v>
+        <v>149510469.41</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>945828.6800000001</v>
+        <v>2388804.18</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>0</v>
@@ -567,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>559835.85</v>
+        <v>848429.96</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>23509179.54</v>
+        <v>45249076.27</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>25014844.07</v>
+        <v>48486310.41</v>
       </c>
     </row>
     <row r="6">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>10504.23</v>
+        <v>27474.6</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>0</v>
@@ -595,13 +595,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>74033.66</v>
+        <v>108354.86</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>22929944.04</v>
+        <v>44390562.3</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>23014481.93</v>
+        <v>44526391.75</v>
       </c>
     </row>
     <row r="7">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>935324.45</v>
+        <v>2361329.58</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>0</v>
@@ -623,13 +623,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>485802.19</v>
+        <v>740075.1</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>579235.5</v>
+        <v>858513.98</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>2000362.14</v>
+        <v>3959918.66</v>
       </c>
     </row>
     <row r="8">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>11437078.73</v>
+        <v>14774708.09</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>0</v>
@@ -651,13 +651,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>3224577.31</v>
+        <v>4770734.66</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>38499312.55</v>
+        <v>70495076.64</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>53160968.59</v>
+        <v>90040519.39</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1462078.73</v>
+        <v>1744823.96</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>0</v>
@@ -679,13 +679,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>2555281.59</v>
+        <v>3791160.81</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>2570238.77</v>
+        <v>10101082.78</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>6587599.09</v>
+        <v>15637067.55</v>
       </c>
     </row>
     <row r="10">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>9975000</v>
+        <v>13029884.13</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -707,13 +707,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>669295.72</v>
+        <v>979573.85</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>27674789</v>
+        <v>50606851.05</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>38319084.72</v>
+        <v>64616309.03</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>8493344.75</v>
+        <v>10466375.76</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>0</v>
@@ -735,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>557855.71</v>
+        <v>820907.52</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>22155034.11</v>
+        <v>40166200.97</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>31206234.57</v>
+        <v>51453484.25</v>
       </c>
     </row>
     <row r="12">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>3633414.29</v>
+        <v>4027963.36</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>0</v>
@@ -763,13 +763,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>66604.27</v>
+        <v>99383.92999999999</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>7126307.17</v>
+        <v>14068778.37</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>10826325.73</v>
+        <v>18196125.67</v>
       </c>
     </row>
     <row r="13">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>4171287.99</v>
+        <v>5288204.42</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>0</v>
@@ -791,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>440150.59</v>
+        <v>646359.76</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>12541966.45</v>
+        <v>22205681.87</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>17153405.03</v>
+        <v>28140246.06</v>
       </c>
     </row>
     <row r="14">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>606644.25</v>
+        <v>992122.41</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>0</v>
@@ -819,13 +819,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>51100.85</v>
+        <v>75163.82000000001</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>2365977.16</v>
+        <v>3650691.14</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>3023722.26</v>
+        <v>4717977.37</v>
       </c>
     </row>
     <row r="15">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>81998.22</v>
+        <v>158085.57</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>0</v>
@@ -850,10 +850,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>120783.33</v>
+        <v>241049.58</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>202781.55</v>
+        <v>399135.15</v>
       </c>
     </row>
     <row r="16">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>1375919.13</v>
+        <v>2563508.37</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>98649.8</v>
+        <v>145876.12</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>5482305.4</v>
+        <v>10440650.08</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>6956874.33</v>
+        <v>13150034.57</v>
       </c>
     </row>
     <row r="17">
@@ -906,10 +906,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>4680836.36</v>
+        <v>6520368.13</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>4680836.36</v>
+        <v>6520368.13</v>
       </c>
     </row>
     <row r="18">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>65343.7</v>
+        <v>279053.63</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>0</v>
@@ -931,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>2570576.02</v>
+        <v>3790960.32</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>3158415.8</v>
+        <v>6913625.65</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>5794335.52</v>
+        <v>10983639.61</v>
       </c>
     </row>
     <row r="19">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>12448251.11</v>
+        <v>17442565.9</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>0</v>
@@ -959,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>6354989.19</v>
+        <v>9410124.939999999</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>65166907.89</v>
+        <v>122657778.56</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>83970148.19</v>
+        <v>149510469.41</v>
       </c>
     </row>
   </sheetData>

--- a/data/informes/cuadro_10_7.xlsx
+++ b/data/informes/cuadro_10_7.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>17442565.9</v>
+        <v>15538027.33</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
@@ -539,13 +539,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>9410124.939999999</v>
+        <v>12125064.7</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>122657778.56</v>
+        <v>119948066.09</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>149510469.41</v>
+        <v>147611158.12</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>2388804.18</v>
+        <v>2144051.24</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>0</v>
@@ -567,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>848429.96</v>
+        <v>1211936.82</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>45249076.27</v>
+        <v>43997103.28</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>48486310.41</v>
+        <v>47353091.34</v>
       </c>
     </row>
     <row r="6">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>27474.6</v>
+        <v>25414.09</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>0</v>
@@ -595,13 +595,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>108354.86</v>
+        <v>433272</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>44390562.3</v>
+        <v>43175250.67</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>44526391.75</v>
+        <v>43633936.77</v>
       </c>
     </row>
     <row r="7">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2361329.58</v>
+        <v>2118637.15</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>0</v>
@@ -623,13 +623,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>740075.1</v>
+        <v>778664.8199999999</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>858513.98</v>
+        <v>821852.61</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>3959918.66</v>
+        <v>3719154.58</v>
       </c>
     </row>
     <row r="8">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>14774708.09</v>
+        <v>13179533.65</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>0</v>
@@ -651,13 +651,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>4770734.66</v>
+        <v>6503784.29</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>70495076.64</v>
+        <v>71004511.06999999</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>90040519.39</v>
+        <v>90687829.01000001</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1744823.96</v>
+        <v>1554711.57</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>0</v>
@@ -679,13 +679,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>3791160.81</v>
+        <v>4817528.75</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>10101082.78</v>
+        <v>8918156.449999999</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>15637067.55</v>
+        <v>15290396.76</v>
       </c>
     </row>
     <row r="10">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>13029884.13</v>
+        <v>11624822.09</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -707,13 +707,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>979573.85</v>
+        <v>1686255.54</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>50606851.05</v>
+        <v>50684749.66</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>64616309.03</v>
+        <v>63995827.29</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>10466375.76</v>
+        <v>9456818.050000001</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>0</v>
@@ -735,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>820907.52</v>
+        <v>1229157.43</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>40166200.97</v>
+        <v>40648328.23</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>51453484.25</v>
+        <v>51334303.71</v>
       </c>
     </row>
     <row r="12">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>4027963.36</v>
+        <v>3533372.67</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>0</v>
@@ -763,13 +763,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>99383.92999999999</v>
+        <v>106346.47</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>14068778.37</v>
+        <v>14395126.21</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>18196125.67</v>
+        <v>18034845.35</v>
       </c>
     </row>
     <row r="13">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>5288204.42</v>
+        <v>4855223.59</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>0</v>
@@ -791,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>646359.76</v>
+        <v>1044095.4</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>22205681.87</v>
+        <v>22475242.72</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>28140246.06</v>
+        <v>28374561.71</v>
       </c>
     </row>
     <row r="14">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>992122.41</v>
+        <v>931128.63</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>0</v>
@@ -819,13 +819,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>75163.82000000001</v>
+        <v>78715.56</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>3650691.14</v>
+        <v>3537148.66</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>4717977.37</v>
+        <v>4546992.85</v>
       </c>
     </row>
     <row r="15">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>158085.57</v>
+        <v>137093.16</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>0</v>
@@ -850,10 +850,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>241049.58</v>
+        <v>240810.64</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>399135.15</v>
+        <v>377903.8</v>
       </c>
     </row>
     <row r="16">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>2563508.37</v>
+        <v>2168004.04</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>145876.12</v>
+        <v>436475.35</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>10440650.08</v>
+        <v>10036421.43</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>13150034.57</v>
+        <v>12640900.81</v>
       </c>
     </row>
     <row r="17">
@@ -906,10 +906,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>6520368.13</v>
+        <v>6564266.94</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>6520368.13</v>
+        <v>6564266.94</v>
       </c>
     </row>
     <row r="18">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>279053.63</v>
+        <v>214442.43</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>0</v>
@@ -931,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>3790960.32</v>
+        <v>4409343.59</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>6913625.65</v>
+        <v>4946451.75</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>10983639.61</v>
+        <v>9570237.77</v>
       </c>
     </row>
     <row r="19">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>17442565.9</v>
+        <v>15538027.33</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>0</v>
@@ -959,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>9410124.939999999</v>
+        <v>12125064.7</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>122657778.56</v>
+        <v>119948066.09</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>149510469.41</v>
+        <v>147611158.12</v>
       </c>
     </row>
   </sheetData>

--- a/data/informes/cuadro_10_7.xlsx
+++ b/data/informes/cuadro_10_7.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>15538027.33</v>
+        <v>15457417.76</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>12125064.7</v>
+        <v>12042747.88</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>119948066.09</v>
+        <v>120110992.48</v>
       </c>
       <c r="H4" s="5" t="n">
         <v>147611158.12</v>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>2144051.24</v>
+        <v>2131904.38</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>0</v>
@@ -567,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>1211936.82</v>
+        <v>1204492.32</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>43997103.28</v>
+        <v>44748319.64</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>47353091.34</v>
+        <v>48084716.34</v>
       </c>
     </row>
     <row r="6">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>25414.09</v>
+        <v>25279.2</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>0</v>
@@ -595,13 +595,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>433272</v>
+        <v>432321.25</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>43175250.67</v>
+        <v>43933794.1</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>43633936.77</v>
+        <v>44391394.54</v>
       </c>
     </row>
     <row r="7">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2118637.15</v>
+        <v>2106625.18</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>0</v>
@@ -623,13 +623,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>778664.8199999999</v>
+        <v>772171.08</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>821852.61</v>
+        <v>814525.54</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>3719154.58</v>
+        <v>3693321.79</v>
       </c>
     </row>
     <row r="8">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>13179533.65</v>
+        <v>13111910.11</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>0</v>
@@ -651,13 +651,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>6503784.29</v>
+        <v>6461923.75</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>71004511.06999999</v>
+        <v>70433731.84999999</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>90687829.01000001</v>
+        <v>90007565.70999999</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1554711.57</v>
+        <v>1547138.95</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>0</v>
@@ -679,13 +679,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>4817528.75</v>
+        <v>4784263.42</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>8918156.449999999</v>
+        <v>8848134.210000001</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>15290396.76</v>
+        <v>15179536.59</v>
       </c>
     </row>
     <row r="10">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>11624822.09</v>
+        <v>11564771.15</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -707,13 +707,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1686255.54</v>
+        <v>1677660.33</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>50684749.66</v>
+        <v>50276817.23</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>63995827.29</v>
+        <v>63519248.72</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>9456818.050000001</v>
+        <v>9406326.880000001</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>0</v>
@@ -735,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1229157.43</v>
+        <v>1221993.34</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>40648328.23</v>
+        <v>40319875.18</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>51334303.71</v>
+        <v>50948195.4</v>
       </c>
     </row>
     <row r="12">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>3533372.67</v>
+        <v>3514864.63</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>0</v>
@@ -763,13 +763,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>106346.47</v>
+        <v>105491.13</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>14395126.21</v>
+        <v>14278984.36</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>18034845.35</v>
+        <v>17899340.12</v>
       </c>
     </row>
     <row r="13">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>4855223.59</v>
+        <v>4828340.82</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>0</v>
@@ -791,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>1044095.4</v>
+        <v>1038442.9</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>22475242.72</v>
+        <v>22293635.15</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>28374561.71</v>
+        <v>28160418.88</v>
       </c>
     </row>
     <row r="14">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>931128.63</v>
+        <v>926677.91</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>0</v>
@@ -819,13 +819,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>78715.56</v>
+        <v>78059.31</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>3537148.66</v>
+        <v>3508399.53</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>4546992.85</v>
+        <v>4513136.76</v>
       </c>
     </row>
     <row r="15">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>137093.16</v>
+        <v>136443.51</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>0</v>
@@ -850,10 +850,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>240810.64</v>
+        <v>238856.13</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>377903.8</v>
+        <v>375299.64</v>
       </c>
     </row>
     <row r="16">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>2168004.04</v>
+        <v>2158444.28</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>436475.35</v>
+        <v>435208.47</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>10036421.43</v>
+        <v>9956942.060000001</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>12640900.81</v>
+        <v>12550594.8</v>
       </c>
     </row>
     <row r="17">
@@ -906,10 +906,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>6564266.94</v>
+        <v>6510392.84</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>6564266.94</v>
+        <v>6510392.84</v>
       </c>
     </row>
     <row r="18">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>214442.43</v>
+        <v>213603.28</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>0</v>
@@ -931,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>4409343.59</v>
+        <v>4376331.8</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4946451.75</v>
+        <v>4928940.99</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>9570237.77</v>
+        <v>9518876.07</v>
       </c>
     </row>
     <row r="19">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>15538027.33</v>
+        <v>15457417.76</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>0</v>
@@ -959,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>12125064.7</v>
+        <v>12042747.88</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>119948066.09</v>
+        <v>120110992.48</v>
       </c>
       <c r="H19" s="9" t="n">
         <v>147611158.12</v>

--- a/data/informes/cuadro_10_7.xlsx
+++ b/data/informes/cuadro_10_7.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>15457417.76</v>
+        <v>16021056.82</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
@@ -539,13 +539,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>12042747.88</v>
+        <v>9656457.710000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>120110992.48</v>
+        <v>123886897.51</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>147611158.12</v>
+        <v>149564412.04</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>2131904.38</v>
+        <v>2532693.8</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>0</v>
@@ -567,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>1204492.32</v>
+        <v>849762.59</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>44748319.64</v>
+        <v>45387830.84</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>48084716.34</v>
+        <v>48770287.24</v>
       </c>
     </row>
     <row r="6">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>25279.2</v>
+        <v>25557.86</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>0</v>
@@ -595,13 +595,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>432321.25</v>
+        <v>117731.28</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>43933794.1</v>
+        <v>44550214.23</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>44391394.54</v>
+        <v>44693503.38</v>
       </c>
     </row>
     <row r="7">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2106625.18</v>
+        <v>2507135.94</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>0</v>
@@ -623,13 +623,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>772171.08</v>
+        <v>732031.3100000001</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>814525.54</v>
+        <v>837616.61</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>3693321.79</v>
+        <v>4076783.85</v>
       </c>
     </row>
     <row r="8">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>13111910.11</v>
+        <v>13262425.33</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>0</v>
@@ -651,13 +651,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>6461923.75</v>
+        <v>5001989.57</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>70433731.84999999</v>
+        <v>73421724.53</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>90007565.70999999</v>
+        <v>91686139.43000001</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1547138.95</v>
+        <v>1562782.3</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>0</v>
@@ -679,13 +679,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>4784263.42</v>
+        <v>3973664.41</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>8848134.210000001</v>
+        <v>9824928.029999999</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>15179536.59</v>
+        <v>15361374.75</v>
       </c>
     </row>
     <row r="10">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>11564771.15</v>
+        <v>11699643.03</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -707,13 +707,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1677660.33</v>
+        <v>1028325.16</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>50276817.23</v>
+        <v>52094352.98</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>63519248.72</v>
+        <v>64822321.17</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>9406326.880000001</v>
+        <v>9521450.4</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>0</v>
@@ -735,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>1221993.34</v>
+        <v>857371.16</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>40319875.18</v>
+        <v>41846637.99</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>50948195.4</v>
+        <v>52225459.54</v>
       </c>
     </row>
     <row r="12">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>3514864.63</v>
+        <v>3553098.17</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>0</v>
@@ -763,13 +763,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>105491.13</v>
+        <v>102173.95</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>14278984.36</v>
+        <v>14840723.32</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>17899340.12</v>
+        <v>18495995.44</v>
       </c>
     </row>
     <row r="13">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>4828340.82</v>
+        <v>4883874.7</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>0</v>
@@ -791,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>1038442.9</v>
+        <v>675210.84</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>22293635.15</v>
+        <v>23006339.11</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>28160418.88</v>
+        <v>28565424.65</v>
       </c>
     </row>
     <row r="14">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>926677.91</v>
+        <v>946691.98</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>0</v>
@@ -819,13 +819,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>78059.31</v>
+        <v>79986.37</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>3508399.53</v>
+        <v>3744228.24</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>4513136.76</v>
+        <v>4770906.58</v>
       </c>
     </row>
     <row r="15">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>136443.51</v>
+        <v>137785.55</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>0</v>
@@ -850,10 +850,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>238856.13</v>
+        <v>255347.32</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>375299.64</v>
+        <v>393132.87</v>
       </c>
     </row>
     <row r="16">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>2158444.28</v>
+        <v>2178192.63</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>435208.47</v>
+        <v>151333.24</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>9956942.060000001</v>
+        <v>10247715</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>12550594.8</v>
+        <v>12577240.87</v>
       </c>
     </row>
     <row r="17">
@@ -906,10 +906,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>6510392.84</v>
+        <v>6620134.38</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>6510392.84</v>
+        <v>6620134.38</v>
       </c>
     </row>
     <row r="18">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>213603.28</v>
+        <v>225937.69</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>0</v>
@@ -931,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>4376331.8</v>
+        <v>3804705.55</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>4928940.99</v>
+        <v>5077342.14</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>9518876.07</v>
+        <v>9107985.380000001</v>
       </c>
     </row>
     <row r="19">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>15457417.76</v>
+        <v>16021056.82</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>0</v>
@@ -959,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>12042747.88</v>
+        <v>9656457.710000001</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>120110992.48</v>
+        <v>123886897.51</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>147611158.12</v>
+        <v>149564412.04</v>
       </c>
     </row>
   </sheetData>

--- a/data/informes/cuadro_10_7.xlsx
+++ b/data/informes/cuadro_10_7.xlsx
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>16021056.82</v>
+        <v>16013821.55</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
@@ -539,13 +539,13 @@
         <v>0</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>9656457.710000001</v>
+        <v>9698145.51</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>123886897.51</v>
+        <v>124002194.07</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>149564412.04</v>
+        <v>149714161.14</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>2532693.8</v>
+        <v>2526005.39</v>
       </c>
       <c r="C5" s="7" t="n">
         <v>0</v>
@@ -567,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>849762.59</v>
+        <v>845629.45</v>
       </c>
       <c r="G5" s="7" t="n">
-        <v>45387830.84</v>
+        <v>45273897.65</v>
       </c>
       <c r="H5" s="7" t="n">
-        <v>48770287.24</v>
+        <v>48645532.48</v>
       </c>
     </row>
     <row r="6">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>25557.86</v>
+        <v>25484.15</v>
       </c>
       <c r="C6" s="7" t="n">
         <v>0</v>
@@ -595,13 +595,13 @@
         <v>0</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>117731.28</v>
+        <v>117211.73</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>44550214.23</v>
+        <v>44440357.54</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>44693503.38</v>
+        <v>44583053.42</v>
       </c>
     </row>
     <row r="7">
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>2507135.94</v>
+        <v>2500521.24</v>
       </c>
       <c r="C7" s="7" t="n">
         <v>0</v>
@@ -623,13 +623,13 @@
         <v>0</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>732031.3100000001</v>
+        <v>728417.71</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>837616.61</v>
+        <v>833540.1</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>4076783.85</v>
+        <v>4062479.05</v>
       </c>
     </row>
     <row r="8">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>13262425.33</v>
+        <v>13262346.85</v>
       </c>
       <c r="C8" s="7" t="n">
         <v>0</v>
@@ -651,13 +651,13 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>5001989.57</v>
+        <v>5065546.59</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>73421724.53</v>
+        <v>73614011.5</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>91686139.43000001</v>
+        <v>91941904.94</v>
       </c>
     </row>
     <row r="9">
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>1562782.3</v>
+        <v>1569441.67</v>
       </c>
       <c r="C9" s="7" t="n">
         <v>0</v>
@@ -679,13 +679,13 @@
         <v>0</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>3973664.41</v>
+        <v>4038485.23</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>9824928.029999999</v>
+        <v>10001299.65</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>15361374.75</v>
+        <v>15609226.55</v>
       </c>
     </row>
     <row r="10">
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>11699643.03</v>
+        <v>11692905.18</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -707,13 +707,13 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>1028325.16</v>
+        <v>1027061.37</v>
       </c>
       <c r="G10" s="7" t="n">
-        <v>52094352.98</v>
+        <v>52171873.39</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>64822321.17</v>
+        <v>64891839.94</v>
       </c>
     </row>
     <row r="11">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="B11" s="7" t="n">
-        <v>9521450.4</v>
+        <v>9492053.5</v>
       </c>
       <c r="C11" s="7" t="n">
         <v>0</v>
@@ -735,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>857371.16</v>
+        <v>853200.29</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>41846637.99</v>
+        <v>41523642.18</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>52225459.54</v>
+        <v>51868895.97</v>
       </c>
     </row>
     <row r="12">
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="B12" s="7" t="n">
-        <v>3553098.17</v>
+        <v>3542310.16</v>
       </c>
       <c r="C12" s="7" t="n">
         <v>0</v>
@@ -763,13 +763,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>102173.95</v>
+        <v>101675.39</v>
       </c>
       <c r="G12" s="7" t="n">
-        <v>14840723.32</v>
+        <v>14745800.75</v>
       </c>
       <c r="H12" s="7" t="n">
-        <v>18495995.44</v>
+        <v>18389786.3</v>
       </c>
     </row>
     <row r="13">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>4883874.7</v>
+        <v>4868205.21</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>0</v>
@@ -791,13 +791,13 @@
         <v>0</v>
       </c>
       <c r="F13" s="7" t="n">
-        <v>675210.84</v>
+        <v>671916.1</v>
       </c>
       <c r="G13" s="7" t="n">
-        <v>23006339.11</v>
+        <v>22810008.08</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>28565424.65</v>
+        <v>28350129.4</v>
       </c>
     </row>
     <row r="14">
@@ -807,7 +807,7 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>946691.98</v>
+        <v>944131.25</v>
       </c>
       <c r="C14" s="7" t="n">
         <v>0</v>
@@ -819,13 +819,13 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>79986.37</v>
+        <v>79608.8</v>
       </c>
       <c r="G14" s="7" t="n">
-        <v>3744228.24</v>
+        <v>3713406.43</v>
       </c>
       <c r="H14" s="7" t="n">
-        <v>4770906.58</v>
+        <v>4737146.48</v>
       </c>
     </row>
     <row r="15">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>137785.55</v>
+        <v>137406.88</v>
       </c>
       <c r="C15" s="7" t="n">
         <v>0</v>
@@ -850,10 +850,10 @@
         <v>0</v>
       </c>
       <c r="G15" s="7" t="n">
-        <v>255347.32</v>
+        <v>254426.92</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>393132.87</v>
+        <v>391833.8</v>
       </c>
     </row>
     <row r="16">
@@ -863,7 +863,7 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>2178192.63</v>
+        <v>2200851.68</v>
       </c>
       <c r="C16" s="7" t="n">
         <v>0</v>
@@ -875,13 +875,13 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>151333.24</v>
+        <v>154336.06</v>
       </c>
       <c r="G16" s="7" t="n">
-        <v>10247715</v>
+        <v>10648231.21</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>12577240.87</v>
+        <v>13003418.95</v>
       </c>
     </row>
     <row r="17">
@@ -906,10 +906,10 @@
         <v>0</v>
       </c>
       <c r="G17" s="7" t="n">
-        <v>6620134.38</v>
+        <v>6580748.42</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>6620134.38</v>
+        <v>6580748.42</v>
       </c>
     </row>
     <row r="18">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>225937.69</v>
+        <v>225469.32</v>
       </c>
       <c r="C18" s="7" t="n">
         <v>0</v>
@@ -931,13 +931,13 @@
         <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>3804705.55</v>
+        <v>3786969.47</v>
       </c>
       <c r="G18" s="7" t="n">
-        <v>5077342.14</v>
+        <v>5114284.93</v>
       </c>
       <c r="H18" s="7" t="n">
-        <v>9107985.380000001</v>
+        <v>9126723.720000001</v>
       </c>
     </row>
     <row r="19">
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>16021056.82</v>
+        <v>16013821.55</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>0</v>
@@ -959,13 +959,13 @@
         <v>0</v>
       </c>
       <c r="F19" s="9" t="n">
-        <v>9656457.710000001</v>
+        <v>9698145.51</v>
       </c>
       <c r="G19" s="9" t="n">
-        <v>123886897.51</v>
+        <v>124002194.07</v>
       </c>
       <c r="H19" s="9" t="n">
-        <v>149564412.04</v>
+        <v>149714161.14</v>
       </c>
     </row>
   </sheetData>
